--- a/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amine s'assoit à table. Maman est près de lui. Dans l'assiette, il y a des petits pois. Ils sont verts. Ils sont ronds. Ça sent le jardin. Amine les regarde. Maman sourit. Maman dit : tu peux goûter. Une petite portion, c'est assez. Amine prend une petite bouchée. Il mâche tout doucement. C'est doux. C'est un peu sucré. Amine dit : c'est doux, maman. Nommer le goût, c'est dire le goût. Maman dit : merci d'avoir goûté. Une petite portion, c'est déjà bien. Amine boit une gorgée d'eau. L'eau est fraîche. Les petits pois restent dans l'assiette.</t>
+          <t>Amine s'assoit à table. Maman est près de lui. Dans l'assiette, il y a des petits pois. Ils sont verts. Ils sont ronds. Ça sent le jardin. Amine les regarde. Maman sourit. Tu peux goûter. Une petite portion, c'est assez. Amine prend une petite bouchée. Il mâche tout doucement. C'est doux. C'est un peu sucré. C'est doux, maman. Nommer le goût, c'est dire le goût. Merci d'avoir goûté. Une petite portion, c'est déjà bien. Amine boit une gorgée d'eau. L'eau est fraîche. Les petits pois restent dans l'assiette.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Amine s'assoit à table. Maman est près de lui. Dans l'assiette, il y a des petits pois. Ils sont verts. Ils sont ronds. Ça sent le jardin. Amine les regarde. Maman sourit.
+maman|Tu peux goûter.
+narrateur|Une petite portion, c'est assez. Amine prend une petite bouchée. Il mâche tout doucement. C'est doux. C'est un peu sucré.
+enfant-f|C'est doux, maman. Nommer le goût, c'est dire le goût.
+maman|Merci d'avoir goûté.
+narrateur|Une petite portion, c'est déjà bien. Amine boit une gorgée d'eau. L'eau est fraîche. Les petits pois restent dans l'assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Amine goûte les petits pois. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Amine a goûté. Il a su nommer le goût. Une petite portion, c'est assez. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Amine range sa cuillère. Il dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Une petite portion, c'est déjà bien. Amine boit une gorgée d'eau. L'eau est fraîche. Les petits pois restent dans l'assiette.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Amine goûte les petits pois. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Amine a goûté. Il a su nommer le goût. Une petite portion, c'est assez. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Amine range sa cuillère. Il dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les petits pois d'Amine</t>
+          <t>Les petits pois d'Aniss</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La passoire tremble au-dessus de l'évier. Les petits pois sautent. Aniss s'assoit. Il goûte une petite bouchée. Il dit le goût à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amine s'assoit à table. Maman est près de lui. Dans l'assiette, il y a des petits pois. Ils sont verts. Ils sont ronds. Ça sent le jardin. Amine les regarde. Maman sourit. Tu peux goûter. Une petite portion, c'est assez. Amine prend une petite bouchée. Il mâche tout doucement. C'est doux. C'est un peu sucré. C'est doux, maman. Nommer le goût, c'est dire le goût. Merci d'avoir goûté. Une petite portion, c'est déjà bien. Amine boit une gorgée d'eau. L'eau est fraîche. Les petits pois restent dans l'assiette.</t>
+          <t>La passoire tremble au-dessus de l'évier. Les petits pois sautent un peu. Ils sont verts. Ils sont ronds. Une goutte tombe. Toc. Ça sent le jardin, un peu. La maison est petite et chaude. Aniss habite ici, avec maman. Un torchon rayé sèche près de la fenêtre. Tu as vu la passoire, Aniss ? Elle tremble, maman. Oui. Les petits pois dansent. On pose la passoire près de l'assiette ? Oui, maman. Maman pose la passoire. Les petits pois restent calmes. En ce moment, Aniss pousse la porte. La porte fait un petit bruit. Viens t'asseoir. Aniss va vers sa chaise. Il tire un peu la chaise. Il s'assoit près de maman. Il pose les pieds par terre. Bravo, Aniss. Tu es bien assis. On est ensemble, à table. Dans l'assiette, des petits pois. Ils sont verts. Ils sont ronds. Ils sont tout ronds, maman. Oui. Comme des petites perles. Tu as bien regardé. Aniss se penche tout près. Ça sent le jardin. Ça sent le jardin, hein ? Oui. Tu veux goûter ? Une petite bouchée. Oui, maman. Aniss prend une petite bouchée. Il goûte. Il mâche tout doucement. Tu mâches bien, tout doux. Un petit pois reste sur la fourchette. Il est tout vert, hein ? Oui, maman. Une goutte glisse sur la vitre. Tu as vu la goutte ? Elle descend, maman. Oui. Tout doux. Tu restes bien assis ? Oui. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1329,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Amine s'assoit à table. Maman est près de lui. Dans l'assiette, il y a des petits pois. Ils sont verts. Ils sont ronds. Ça sent le jardin. Amine les regarde. Maman sourit.
-maman|Tu peux goûter.
-narrateur|Une petite portion, c'est assez. Amine prend une petite bouchée. Il mâche tout doucement. C'est doux. C'est un peu sucré.
-enfant-f|C'est doux, maman. Nommer le goût, c'est dire le goût.
-maman|Merci d'avoir goûté.
-narrateur|Une petite portion, c'est déjà bien. Amine boit une gorgée d'eau. L'eau est fraîche. Les petits pois restent dans l'assiette.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La passoire tremble au-dessus de l'évier.
+narrateur|Les petits pois sautent un peu.
+narrateur|Ils sont verts.
+narrateur|Ils sont ronds.
+narrateur|Une goutte tombe.
+narrateur|Toc.
+narrateur|Ça sent le jardin, un peu.
+narrateur|La maison est petite et chaude.
+narrateur|Aniss habite ici, avec maman.
+narrateur|Un torchon rayé sèche près de la fenêtre.
+maman|Tu as vu la passoire, Aniss ?
+enfant-m|Elle tremble, maman.
+maman|Oui.
+maman|Les petits pois dansent.
+maman|On pose la passoire près de l'assiette ?
+enfant-m|Oui, maman.
+narrateur|Maman pose la passoire.
+narrateur|Les petits pois restent calmes.
+narrateur|En ce moment, Aniss pousse la porte.
+narrateur|La porte fait un petit bruit.
+maman|Viens t'asseoir.
+narrateur|Aniss va vers sa chaise.
+narrateur|Il tire un peu la chaise.
+narrateur|Il s'assoit près de maman.
+narrateur|Il pose les pieds par terre.
+maman|Bravo, Aniss.
+maman|Tu es bien assis.
+maman|On est ensemble, à table.
+narrateur|Dans l'assiette, des petits pois.
+narrateur|Ils sont verts.
+narrateur|Ils sont ronds.
+enfant-m|Ils sont tout ronds, maman.
+maman|Oui.
+maman|Comme des petites perles.
+maman|Tu as bien regardé.
+narrateur|Aniss se penche tout près.
+narrateur|Ça sent le jardin.
+maman|Ça sent le jardin, hein ?
+enfant-m|Oui.
+maman|Tu veux goûter ?
+maman|Une petite bouchée.
+enfant-m|Oui, maman.
+narrateur|Aniss prend une petite bouchée.
+narrateur|Il goûte.
+narrateur|Il mâche tout doucement.
+maman|Tu mâches bien, tout doux.
+narrateur|Un petit pois reste sur la fourchette.
+maman|Il est tout vert, hein ?
+enfant-m|Oui, maman.
+narrateur|Une goutte glisse sur la vitre.
+maman|Tu as vu la goutte ?
+enfant-m|Elle descend, maman.
+maman|Oui. Tout doux.
+maman|Tu restes bien assis ?
+enfant-m|Oui.
+maman|Bravo.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>passoire,assiette</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1416,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amine goûte les petits pois. Que fait-il ?</t>
+          <t>Aniss goûte les petits pois. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Amine goûte les petits pois. Que fait-il ?</t>
+          <t>narrateur|Aniss goûte les petits pois.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amine a goûté. Il a su nommer le goût. Une petite portion, c'est assez. Maman est là.</t>
+          <t>Aniss mâche encore un peu. Il est toujours assis. C'est doux, maman. C'est un peu sucré. Oui. Doux et sucré. Bravo. Tu as nommé le goût. C'est du bon travail. Une petite portion reste dans l'assiette. Tu as fini ta petite bouchée ? Oui. Le reste peut attendre. Une petite portion, c'est assez. Aniss pose sa fourchette. Merci d'avoir goûté.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1745,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amine a goûté. Il a su nommer le goût. Une petite portion, c'est assez. Maman est là.</t>
+          <t>narrateur|Aniss mâche encore un peu.
+narrateur|Il est toujours assis.
+enfant-m|C'est doux, maman.
+enfant-m|C'est un peu sucré.
+maman|Oui.
+maman|Doux et sucré.
+maman|Bravo.
+maman|Tu as nommé le goût.
+maman|C'est du bon travail.
+narrateur|Une petite portion reste dans l'assiette.
+maman|Tu as fini ta petite bouchée ?
+enfant-m|Oui.
+maman|Le reste peut attendre.
+maman|Une petite portion, c'est assez.
+narrateur|Aniss pose sa fourchette.
+maman|Merci d'avoir goûté.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amine range sa cuillère. Il dit merci à maman.</t>
+          <t>Tu veux un peu d'eau ? Oui, maman. Maman verse de l'eau. L'eau fait un petit bruit. Aniss boit une gorgée. L'eau est fraîche. Merci, maman. Merci, Aniss. On reste encore un peu ensemble ? Oui. Aniss reste assis. La cuisine est calme. Tu es encore bien assis. Bravo. Les petits pois restent dans l'assiette. Tu as fini de ranger ta fourchette ? Oui, maman. La passoire ne tremble plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,7 +1924,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Amine range sa cuillère. Il dit merci à maman.</t>
+          <t>maman|Tu veux un peu d'eau ?
+enfant-m|Oui, maman.
+narrateur|Maman verse de l'eau.
+narrateur|L'eau fait un petit bruit.
+narrateur|Aniss boit une gorgée.
+narrateur|L'eau est fraîche.
+enfant-m|Merci, maman.
+maman|Merci, Aniss.
+maman|On reste encore un peu ensemble ?
+enfant-m|Oui.
+narrateur|Aniss reste assis.
+narrateur|La cuisine est calme.
+maman|Tu es encore bien assis.
+maman|Bravo.
+narrateur|Les petits pois restent dans l'assiette.
+maman|Tu as fini de ranger ta fourchette ?
+enfant-m|Oui, maman.
+narrateur|La passoire ne tremble plus.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1865,7 +1969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai goûté une petite bouchée. C'était doux. Bravo. Tu as fait du bon travail. On était assis, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2109,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai goûté une petite bouchée.
+enfant-m|C'était doux.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|On était assis, ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2174,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amine s'assoit à table. Maman est près de lui. Dans l'assiette, il y a des petits pois. Ils sont verts. Ils sont ronds. Ça sent le jardin. Amine les regarde. Maman sourit. Maman dit : tu peux &lt;emphasis level="moderate"&gt;goûter&lt;/emphasis&gt;. Une petite portion, c'est assez. Amine prend une petite bouchée. Il mâche tout doucement. C'est doux. C'est un peu sucré. Amine dit : c'est doux, maman. Nommer le goût, c'est dire le goût. Maman dit : merci d'avoir goûté. Une petite portion, c'est déjà bien. Amine boit une gorgée d'eau. L'eau est fraîche. Les petits pois restent dans l'assiette.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La passoire tremble au-dessus de l'évier. Les petits pois sautent un peu. Ils sont verts. Ils sont ronds. Une goutte tombe. Toc. Ça sent le jardin, un peu. La maison est petite et chaude. Aniss habite ici, avec maman. Un torchon rayé sèche près de la fenêtre. Tu as vu la passoire, Aniss ? Elle tremble, maman. Oui. Les petits pois dansent. On pose la passoire près de l'assiette ? Oui, maman. Maman pose la passoire. Les petits pois restent calmes. En ce moment, Aniss pousse la porte. La porte fait un petit bruit. Viens t'asseoir. Aniss va vers sa chaise. Il tire un peu la chaise. Il s'assoit près de maman. Il pose les pieds par terre. Bravo, Aniss. Tu es bien assis. On est ensemble, à table. Dans l'assiette, des petits pois. Ils sont verts. Ils sont ronds. Ils sont tout ronds, maman. Oui. Comme des petites perles. Tu as bien regardé. Aniss se penche tout près. Ça sent le jardin. Ça sent le jardin, hein ? Oui. Tu veux goûter ? Une petite bouchée. Oui, maman. Aniss prend une petite bouchée. Il goûte. Il mâche tout doucement. Tu mâches bien, tout doux. Un petit pois reste sur la fourchette. Il est tout vert, hein ? Oui, maman. Une goutte glisse sur la vitre. Tu as vu la goutte ? Elle descend, maman. Oui. Tout doux. Tu restes bien assis ? Oui. Bravo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amine goûte les petits pois. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss goûte les petits pois. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1576,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss mâche encore un peu. Il est toujours assis. C'est doux, maman. C'est un peu sucré. Oui. Doux et sucré. Bravo. Tu as nommé le goût. C'est du bon travail. Une petite portion reste dans l'assiette. Tu as fini ta petite bouchée ? Oui. Le reste peut attendre. Une petite portion, c'est assez. Aniss pose sa fourchette. Merci d'avoir goûté.</t>
+          <t>Aniss mâche encore un peu. Il est toujours assis. C'est doux, maman. C'est un peu sucré. Oui. Doux et sucré. Bravo. Tu as nommé le goût. Une petite portion reste dans l'assiette. Tu as fini ta petite bouchée ? Oui. Le reste peut attendre. Une petite portion, c'est assez. Aniss pose sa fourchette. Merci d'avoir goûté.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amine a goûté. Il a su nommer le goût. Une &lt;emphasis level="moderate"&gt;petite&lt;/emphasis&gt; portion, c'est assez. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss mâche encore un peu. Il est toujours assis. C'est doux, maman. C'est un peu sucré. Oui. Doux et sucré. Bravo. Tu as nommé le goût. Une petite portion reste dans l'assiette. Tu as fini ta petite bouchée ? Oui. Le reste peut attendre. Une petite portion, c'est assez. Aniss pose sa fourchette. Merci d'avoir goûté.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1753,7 +1752,6 @@
 maman|Doux et sucré.
 maman|Bravo.
 maman|Tu as nommé le goût.
-maman|C'est du bon travail.
 narrateur|Une petite portion reste dans l'assiette.
 maman|Tu as fini ta petite bouchée ?
 enfant-m|Oui.
@@ -1763,7 +1761,6 @@
 maman|Merci d'avoir goûté.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1788,12 +1785,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tu veux un peu d'eau ? Oui, maman. Maman verse de l'eau. L'eau fait un petit bruit. Aniss boit une gorgée. L'eau est fraîche. Merci, maman. Merci, Aniss. On reste encore un peu ensemble ? Oui. Aniss reste assis. La cuisine est calme. Tu es encore bien assis. Bravo. Les petits pois restent dans l'assiette. Tu as fini de ranger ta fourchette ? Oui, maman. La passoire ne tremble plus.</t>
+          <t>Tu veux un peu d'eau ? Oui, maman. Maman verse de l'eau. L'eau fait un petit bruit. Aniss boit une gorgée. L'eau est fraîche. Merci, maman. Merci, Aniss. On reste encore un peu ensemble ? Oui. Aniss reste assis. La cuisine est calme. Tu es encore bien assis. Bravo. Les petits pois restent dans l'assiette. Tu as fini de ranger ta fourchette ? Oui, maman. La passoire ne tremble plus. Tu as nommé le goût. C'était doux. Bravo, Aniss. Le torchon rayé sèche encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amine range sa cuillère. Il dit merci à maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu veux un peu d'eau ? Oui, maman. Maman verse de l'eau. L'eau fait un petit bruit. Aniss boit une gorgée. L'eau est fraîche. Merci, maman. Merci, Aniss. On reste encore un peu ensemble ? Oui. Aniss reste assis. La cuisine est calme. Tu es encore bien assis. Bravo. Les petits pois restent dans l'assiette. Tu as fini de ranger ta fourchette ? Oui, maman. La passoire ne tremble plus. Tu as nommé le goût. C'était doux. Bravo, Aniss. Le torchon rayé sèche encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,10 +1938,13 @@
 narrateur|Les petits pois restent dans l'assiette.
 maman|Tu as fini de ranger ta fourchette ?
 enfant-m|Oui, maman.
-narrateur|La passoire ne tremble plus.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|La passoire ne tremble plus.
+maman|Tu as nommé le goût.
+enfant-m|C'était doux.
+maman|Bravo, Aniss.
+narrateur|Le torchon rayé sèche encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai goûté une petite bouchée. C'était doux. Bravo. Tu as fait du bon travail. On était assis, ensemble. L'histoire est finie.</t>
+          <t>J'ai goûté une petite bouchée. C'était doux. Bravo. On était assis, ensemble.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai goûté une petite bouchée. C'était doux. Bravo. On était assis, ensemble.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2112,12 +2112,9 @@
           <t>enfant-m|J'ai goûté une petite bouchée.
 enfant-m|C'était doux.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-maman|On était assis, ensemble.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|On était assis, ensemble.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2136,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2181,6 +2178,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-04.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amine, maman</t>
+          <t>Aniss, maman</t>
         </is>
       </c>
     </row>
